--- a/CB-Achmea/2021/Uitsluitingen.xlsx
+++ b/CB-Achmea/2021/Uitsluitingen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/CB-Achmea/2021/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D961A237-A088-4BA4-92AE-032AFAF1271A}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA7338BF-C1BF-559F-BD35-63AD13B36C56}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Achmea" sheetId="1" r:id="rId1"/>
@@ -11140,7 +11140,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
